--- a/data/trans_orig/Q5409A_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5409A_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si necesita sonda u otros dispositivos y es capaz de utilizarlos en 2023</t>
+          <t>Población según si necesita sonda u otros dispositivos y es capaz de utilizarlos en 2023 (tasa de respuesta: 96,39%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15533</t>
+          <t>15391</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8254</t>
+          <t>7722</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18111</t>
+          <t>17663</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15425</t>
+          <t>14882</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24002</t>
+          <t>23953</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50672</t>
+          <t>50918</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64935</t>
+          <t>64405</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>65,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68601</t>
+          <t>68633</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85904</t>
+          <t>85402</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,06%</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6620</t>
+          <t>6732</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9767</t>
+          <t>9766</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19862</t>
+          <t>20309</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12729</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24841</t>
+          <t>24024</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14612</t>
+          <t>14961</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8312</t>
+          <t>8334</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18394</t>
+          <t>18383</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16867</t>
+          <t>16126</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>29249</t>
+          <t>30013</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>2932</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>397</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t>4359</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9512</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17575</t>
+          <t>17503</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12043</t>
+          <t>12066</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18925</t>
+          <t>18529</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23307</t>
+          <t>24095</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34345</t>
+          <t>34893</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>68,44%</t>
         </is>
       </c>
     </row>
@@ -1638,97 +1638,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1140</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1184</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>4030</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4,57%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>16,14%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>3916</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>4,57%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>4307</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>15,69%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>1140</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>4054</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6701</t>
+          <t>6444</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1863</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7325</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11862</t>
+          <t>11954</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12825</t>
+          <t>12770</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>6248</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8361</t>
+          <t>8242</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17804</t>
+          <t>17379</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -2094,97 +2094,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1174</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1033</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3591</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>16,23%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>18,74%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>49,62%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1174</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>16,23%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3783</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>9,21%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>44,65%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3553</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>9,21%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>29,68%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>7249</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>56,87%</t>
         </is>
       </c>
     </row>
@@ -2320,97 +2320,97 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>1033</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>18,74%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>856</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>971</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>959</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,62 +2468,62 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>856</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>1098</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>797</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>2143</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5358</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4259</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9425</t>
+          <t>9275</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>72,76%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17848</t>
+          <t>17712</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10294</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21070</t>
+          <t>21715</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28647</t>
+          <t>28398</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41147</t>
+          <t>40889</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>67468</t>
+          <t>68714</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>83675</t>
+          <t>84529</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>100376</t>
+          <t>100352</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>121143</t>
+          <t>120653</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,23%</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7816</t>
+          <t>8228</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8573</t>
+          <t>8741</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11120</t>
+          <t>11157</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13543</t>
+          <t>13195</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25210</t>
+          <t>25089</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19359</t>
+          <t>18027</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31708</t>
+          <t>32054</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16704</t>
+          <t>16957</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>29221</t>
+          <t>29017</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13540</t>
+          <t>13549</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24762</t>
+          <t>25310</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>33391</t>
+          <t>32813</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>50488</t>
+          <t>50679</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5409A_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q5409A_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1823</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>656</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4338</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10421</t>
+          <t>11515</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15391</t>
+          <t>18466</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12266</t>
+          <t>13339</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7722</t>
+          <t>8503</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17663</t>
+          <t>19712</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19521</t>
+          <t>20810</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14882</t>
+          <t>15649</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23953</t>
+          <t>24991</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>57536</t>
+          <t>61538</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50918</t>
+          <t>53236</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64405</t>
+          <t>69318</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,83%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>77057</t>
+          <t>82347</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>68633</t>
+          <t>73292</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85402</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>63,23%</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>680</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -961,12 +961,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3270</t>
+          <t>4091</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,22 +986,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>6976</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3564</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7262</t>
+          <t>7722</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3430</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1574</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6732</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14380</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9766</t>
+          <t>11237</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20309</t>
+          <t>23500</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>17810</t>
+          <t>20463</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12484</t>
+          <t>14747</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24024</t>
+          <t>28755</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10080</t>
+          <t>10853</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>6765</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14961</t>
+          <t>15573</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>12542</t>
+          <t>14151</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8334</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18383</t>
+          <t>20214</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,27 +1247,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>22622</t>
+          <t>25004</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16126</t>
+          <t>18189</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30013</t>
+          <t>32653</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>37845</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>37845</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>37845</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>97842</t>
+          <t>107245</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>97842</t>
+          <t>107245</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>97842</t>
+          <t>107245</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>133319</t>
+          <t>145090</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>133319</t>
+          <t>145090</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>133319</t>
+          <t>145090</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>610</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>881</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>1490</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>429</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>4681</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13523</t>
+          <t>14776</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9132</t>
+          <t>10375</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17503</t>
+          <t>19220</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>68,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15575</t>
+          <t>17746</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12066</t>
+          <t>13772</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18529</t>
+          <t>21376</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>29097</t>
+          <t>32522</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24095</t>
+          <t>26682</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34893</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,25%</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4307</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6444</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>2176</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>8160</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7019</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>4390</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11954</t>
+          <t>12867</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8882</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5255</t>
+          <t>5503</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12770</t>
+          <t>13922</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>3688</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6248</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>12254</t>
+          <t>12992</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8242</t>
+          <t>8936</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17379</t>
+          <t>18638</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,15%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>26024</t>
+          <t>28010</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26024</t>
+          <t>28010</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26024</t>
+          <t>28010</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>24963</t>
+          <t>28206</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24963</t>
+          <t>28206</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24963</t>
+          <t>28206</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>50987</t>
+          <t>56216</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>50987</t>
+          <t>56216</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>50987</t>
+          <t>56216</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3783</t>
+          <t>4354</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>28,81%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4585</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>8559</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,63%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>659</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>659</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>23,0%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2143</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2763</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>5255</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6830</t>
+          <t>7782</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4710</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>9275</t>
+          <t>10760</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>71,19%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>8257</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>8257</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>8257</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>12748</t>
+          <t>15115</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>12748</t>
+          <t>15115</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12748</t>
+          <t>15115</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>923</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>12440</t>
+          <t>13717</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>8743</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17712</t>
+          <t>19731</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>14918</t>
+          <t>16150</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10497</t>
+          <t>10569</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21715</t>
+          <t>22875</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>34330</t>
+          <t>36958</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28398</t>
+          <t>29712</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40889</t>
+          <t>44015</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>76410</t>
+          <t>83265</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>68714</t>
+          <t>74264</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>84529</t>
+          <t>91724</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>51,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>110740</t>
+          <t>120223</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>100352</t>
+          <t>107504</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>120653</t>
+          <t>130927</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>60,5%</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>680</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3007,12 +3007,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8228</t>
+          <t>9509</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>4703</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2457</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>8741</t>
+          <t>10225</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>6575</t>
+          <t>7658</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11157</t>
+          <t>12596</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>18412</t>
+          <t>21312</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13195</t>
+          <t>14812</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25089</t>
+          <t>28482</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>24987</t>
+          <t>28969</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18027</t>
+          <t>21162</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32054</t>
+          <t>37634</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -3223,17 +3223,17 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>23029</t>
+          <t>24985</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16957</t>
+          <t>18642</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>29017</t>
+          <t>32158</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>18678</t>
+          <t>20794</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>13549</t>
+          <t>14923</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25310</t>
+          <t>28472</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>41706</t>
+          <t>45779</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>32813</t>
+          <t>36402</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>50679</t>
+          <t>56194</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>67012</t>
+          <t>72713</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>67012</t>
+          <t>72713</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>67012</t>
+          <t>72713</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>130042</t>
+          <t>143708</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>130042</t>
+          <t>143708</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>130042</t>
+          <t>143708</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>197054</t>
+          <t>216421</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>197054</t>
+          <t>216421</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>197054</t>
+          <t>216421</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
